--- a/therapist_forms/017_reiki_consent_form--therapist_forms.xlsx
+++ b/therapist_forms/017_reiki_consent_form--therapist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'eggs'}</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'eggs'}</t>
+          <t>eggs</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'tree_nuts'}</t>
+          <t>tree_nuts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'tree_nuts'}</t>
+          <t>tree nuts</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'wheat'}</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'wheat'}</t>
+          <t>wheat</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
     </row>
@@ -1054,114 +1054,114 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'shellfish'}</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'shellfish'}</t>
+          <t>beef</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'dairy'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'dairy'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'beef'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'beef'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>emergency_contact_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>emergency_contact_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>medical_history_chronic_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>diabetes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>medical_history_chronic_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>high blood pressure</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'diabetes'}</t>
+          <t>high cholesterol</t>
         </is>
       </c>
     </row>
@@ -1190,46 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'high_blood_pressure'}</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'high_blood_pressure'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medical_history_chronic_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'high_cholesterol'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'high_cholesterol'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>medical_history_chronic_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'cancer'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'cancer'}</t>
+          <t>cancer</t>
         </is>
       </c>
     </row>
